--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260715.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>344,670,039</t>
+          <t>14,759,547</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,759,547</t>
+          <t>344,670,039</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>108,061,653</t>
+          <t>1,247,763</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,247,763</t>
+          <t>108,061,653</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
